--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487770_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487770_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7223</v>
+        <v>7.4977</v>
       </c>
       <c r="E2" t="n">
-        <v>3.798</v>
+        <v>3.6908</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9244</v>
+        <v>3.8069</v>
       </c>
       <c r="G2" t="n">
         <v>4.5113</v>
@@ -610,13 +610,13 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5461</v>
+        <v>0.3215</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.1757</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6146</v>
+        <v>0.4972</v>
       </c>
       <c r="V2" t="n">
         <v>0.5838</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3686</v>
+        <v>3.9091</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0386</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>4.33</v>
+        <v>3.9777</v>
       </c>
       <c r="G3" t="n">
         <v>3.0192</v>
@@ -688,13 +688,13 @@
         <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7438</v>
+        <v>0.2843</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2643</v>
+        <v>-0.3714</v>
       </c>
       <c r="U3" t="n">
-        <v>1.008</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>0.8137</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3173</v>
+        <v>3.3085</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3648</v>
+        <v>2.1505</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9525</v>
+        <v>1.158</v>
       </c>
       <c r="G4" t="n">
         <v>1.674</v>
@@ -766,13 +766,13 @@
         <v>1.2487</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0189</v>
+        <v>0.0101</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1272</v>
+        <v>-0.0871</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1083</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0.5838</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4538</v>
+        <v>2.7269</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0169</v>
+        <v>0.2312</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4369</v>
+        <v>2.4956</v>
       </c>
       <c r="G5" t="n">
         <v>0.0731</v>
@@ -844,13 +844,13 @@
         <v>2.0812</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6381</v>
+        <v>-0.365</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7177</v>
+        <v>-0.5034</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0796</v>
+        <v>0.1383</v>
       </c>
       <c r="V5" t="n">
         <v>0.9376</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8249</v>
+        <v>2.2447</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1438</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9687</v>
+        <v>2.1742</v>
       </c>
       <c r="G6" t="n">
         <v>5.5919</v>
@@ -922,13 +922,13 @@
         <v>2.0812</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7483</v>
+        <v>-0.3285</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7829</v>
+        <v>-0.5686</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0346</v>
+        <v>0.2401</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9376</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.09470000000000001</v>
+        <v>0.0418</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.0419</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0294</v>
+        <v>-0.0001</v>
       </c>
       <c r="G7" t="n">
         <v>0.0939</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1885</v>
+        <v>-0.052</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.0419</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1233</v>
+        <v>-0.0939</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. SCHUTTE</t>
+          <t>N. SAGNIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3176</v>
+        <v>-0.497</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4858</v>
+        <v>-4.0575</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8034</v>
+        <v>3.5605</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0545</v>
+        <v>1.0985</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5689</v>
+        <v>-1.1622</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5143</v>
+        <v>2.2607</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1569</v>
+        <v>-1.2772</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9609</v>
+        <v>-1.3948</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1959</v>
+        <v>0.1176</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1023</v>
+        <v>2.3757</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3921</v>
+        <v>0.2326</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7103</v>
+        <v>2.1431</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.2487</v>
+        <v>0.4162</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2893</v>
+        <v>-2.0812</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0406</v>
+        <v>2.4974</v>
       </c>
       <c r="S8" t="n">
-        <v>1.7954</v>
+        <v>-0.6142</v>
       </c>
       <c r="T8" t="n">
-        <v>0.972</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8234</v>
+        <v>0.0849</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.9188</v>
+        <v>-1.3975</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.565</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ AGUILAR</t>
+          <t>G. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3342</v>
+        <v>-0.5891</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5228</v>
+        <v>-1.5509</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1886</v>
+        <v>0.9618</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6592</v>
+        <v>-1.0307</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.5074</v>
+        <v>-2.1901</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8483000000000001</v>
+        <v>1.1593</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2303</v>
+        <v>-1.2837</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.6826</v>
+        <v>-1.9409</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4523</v>
+        <v>0.6572</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4289</v>
+        <v>0.2529</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8248</v>
+        <v>-0.2492</v>
       </c>
       <c r="O9" t="n">
-        <v>0.396</v>
+        <v>0.5021</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="R9" t="n">
         <v>1.6649</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3399</v>
+        <v>-0.0776</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.46</v>
+        <v>-0.2891</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1201</v>
+        <v>0.2114</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.9376</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X9" t="n">
         <v>-1.1675</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. SAGNIA</t>
+          <t>A. RODRIGUEZ AGUILAR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7994</v>
+        <v>-0.5969</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2718</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4724</v>
+        <v>0.2474</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0985</v>
+        <v>-1.6592</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1622</v>
+        <v>-2.5074</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2607</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2772</v>
+        <v>-1.2303</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3948</v>
+        <v>-1.6826</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1176</v>
+        <v>0.4523</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3757</v>
+        <v>-0.4289</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2326</v>
+        <v>-0.8248</v>
       </c>
       <c r="O10" t="n">
-        <v>2.1431</v>
+        <v>0.396</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4162</v>
+        <v>1.6649</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4974</v>
+        <v>1.6649</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9166</v>
+        <v>-0.6027</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9134</v>
+        <v>-0.7815</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0032</v>
+        <v>0.1788</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3975</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.3975</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. OROZCO DOMINGUEZ</t>
+          <t>K. SCHUTTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9003</v>
+        <v>-1.2541</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9795</v>
+        <v>0.8429</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0792</v>
+        <v>-2.097</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0307</v>
+        <v>2.0545</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1901</v>
+        <v>2.5689</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1593</v>
+        <v>-0.5143</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2837</v>
+        <v>3.1569</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9409</v>
+        <v>2.9609</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6572</v>
+        <v>0.1959</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2529</v>
+        <v>-1.1023</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2492</v>
+        <v>-0.3921</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5021</v>
+        <v>-0.7103</v>
       </c>
       <c r="P11" t="n">
-        <v>1.4568</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2081</v>
+        <v>-2.2893</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3888</v>
+        <v>0.8589</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7177</v>
+        <v>0.3291</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3289</v>
+        <v>0.5298</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9376</v>
+        <v>-2.9188</v>
       </c>
       <c r="W11" t="n">
-        <v>0.23</v>
+        <v>-0.3538</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1675</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0878</v>
+        <v>-1.8633</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6782</v>
+        <v>-0.571</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4097</v>
+        <v>-1.2923</v>
       </c>
       <c r="G12" t="n">
         <v>-0.536</v>
@@ -1390,13 +1390,13 @@
         <v>1.6649</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6518</v>
+        <v>-0.4272</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.48</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0646</v>
+        <v>0.0529</v>
       </c>
       <c r="V12" t="n">
         <v>-2.565</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.3335</v>
+        <v>-3.1089</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9611</v>
+        <v>-2.854</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3724</v>
+        <v>-0.2549</v>
       </c>
       <c r="G13" t="n">
         <v>-1.2965</v>
@@ -1468,13 +1468,13 @@
         <v>0.4162</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5989</v>
+        <v>-0.3743</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3915</v>
+        <v>-0.2843</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2075</v>
+        <v>-0.09</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8137</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.8194</v>
+        <v>11.81939999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.918299999999999</v>
+        <v>-2.9185</v>
       </c>
       <c r="F14" t="n">
         <v>14.7378</v>
@@ -1513,7 +1513,7 @@
         <v>13.594</v>
       </c>
       <c r="H14" t="n">
-        <v>0.04149999999999965</v>
+        <v>0.04150000000000009</v>
       </c>
       <c r="I14" t="n">
         <v>13.5527</v>
@@ -1525,7 +1525,7 @@
         <v>2.757499999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>5.674200000000001</v>
+        <v>5.6742</v>
       </c>
       <c r="M14" t="n">
         <v>5.162599999999999</v>
@@ -1549,16 +1549,16 @@
         <v>-1.3667</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.869200000000001</v>
+        <v>-3.8692</v>
       </c>
       <c r="U14" t="n">
-        <v>2.5023</v>
+        <v>2.5024</v>
       </c>
       <c r="V14" t="n">
         <v>-6.6513</v>
       </c>
       <c r="W14" t="n">
-        <v>5.006200000000001</v>
+        <v>5.0062</v>
       </c>
       <c r="X14" t="n">
         <v>-11.6575</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8885</v>
+        <v>3.5656</v>
       </c>
       <c r="E15" t="n">
         <v>3.4141</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4745</v>
+        <v>0.1515</v>
       </c>
       <c r="G15" t="n">
         <v>0.5790999999999999</v>
@@ -1624,13 +1624,13 @@
         <v>2.2893</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1638</v>
+        <v>-0.1592</v>
       </c>
       <c r="T15" t="n">
         <v>-0.3948</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5585</v>
+        <v>0.2356</v>
       </c>
       <c r="V15" t="n">
         <v>2.1051</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8577</v>
+        <v>3.1164</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6146</v>
+        <v>2.0788</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2431</v>
+        <v>1.0376</v>
       </c>
       <c r="G16" t="n">
         <v>0.3122</v>
@@ -1702,13 +1702,13 @@
         <v>2.0812</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7078</v>
+        <v>-0.0334</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2544</v>
+        <v>-0.2814</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4535</v>
+        <v>0.248</v>
       </c>
       <c r="V16" t="n">
         <v>4.0863</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7921</v>
+        <v>0.8699</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1305</v>
+        <v>0.2376</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6616</v>
+        <v>0.6322</v>
       </c>
       <c r="G17" t="n">
         <v>0.2649</v>
@@ -1780,13 +1780,13 @@
         <v>0.4162</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1109</v>
+        <v>0.1887</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1957</v>
+        <v>-0.0886</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3066</v>
+        <v>0.2773</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. SALAS MERCHAN</t>
+          <t>C. KNOWLES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1022</v>
+        <v>-0.2772</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3648</v>
+        <v>-1.8887</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2626</v>
+        <v>1.6115</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.0733</v>
+        <v>-0.2867</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8355</v>
+        <v>0.2987</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.2378</v>
+        <v>-0.5854</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.1871</v>
+        <v>-0.6866</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6228</v>
+        <v>0.1151</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.5643</v>
+        <v>-0.8017</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8862</v>
+        <v>0.3999</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2126</v>
+        <v>0.1836</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6735</v>
+        <v>0.2164</v>
       </c>
       <c r="P18" t="n">
-        <v>1.2487</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.2487</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4974</v>
+        <v>0.6244</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7223</v>
+        <v>0.1957</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9035</v>
+        <v>-0.3915</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8188</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. KNOWLES</t>
+          <t>R. SALAS MERCHAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-1.2134</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8887</v>
+        <v>-2.3292</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2592</v>
+        <v>1.1158</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2867</v>
+        <v>-3.0733</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2987</v>
+        <v>-0.8355</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5854</v>
+        <v>-2.2378</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6866</v>
+        <v>-2.1871</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1151</v>
+        <v>-0.6228</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.8017</v>
+        <v>-1.5643</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3999</v>
+        <v>-0.8862</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1836</v>
+        <v>-0.2126</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2164</v>
+        <v>-0.6735</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0406</v>
+        <v>-1.2487</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6244</v>
+        <v>2.4974</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1566</v>
+        <v>0.6111</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3915</v>
+        <v>-0.0609</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2349</v>
+        <v>0.672</v>
       </c>
       <c r="V19" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. SIMA FATTY</t>
+          <t>J. CERA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6298</v>
+        <v>-1.2309</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7166</v>
+        <v>-1.4993</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0867</v>
+        <v>0.2684</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3129</v>
+        <v>-4.55</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2067</v>
+        <v>-0.4499</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1063</v>
+        <v>-4.1001</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3904</v>
+        <v>-3.7334</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0384</v>
+        <v>-0.2007</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4287</v>
+        <v>-3.5327</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0775</v>
+        <v>-0.8166</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.245</v>
+        <v>-0.2492</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3225</v>
+        <v>-0.5674</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0587</v>
+        <v>-0.0785</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3262</v>
+        <v>-0.331</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3849</v>
+        <v>0.2525</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5838</v>
+        <v>2.565</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.565</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. CERA RODRIGUEZ</t>
+          <t>O. SIMA FATTY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8754</v>
+        <v>-1.3275</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8208</v>
+        <v>-1.5023</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0546</v>
+        <v>0.1748</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.55</v>
+        <v>-1.3129</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4499</v>
+        <v>-0.2067</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.1001</v>
+        <v>-1.1063</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.7334</v>
+        <v>-1.3904</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2007</v>
+        <v>0.0384</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.5327</v>
+        <v>-1.4287</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8166</v>
+        <v>0.0775</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2492</v>
+        <v>-0.245</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5674</v>
+        <v>0.3225</v>
       </c>
       <c r="P21" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7229</v>
+        <v>0.3611</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6524</v>
+        <v>-0.1119</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0704</v>
+        <v>0.473</v>
       </c>
       <c r="V21" t="n">
-        <v>2.565</v>
+        <v>-0.5838</v>
       </c>
       <c r="W21" t="n">
-        <v>2.565</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. EFAMBE</t>
+          <t>R. BLAK MOLLER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4621</v>
+        <v>-2.4181</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0712</v>
+        <v>-0.5522</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6091</v>
+        <v>-1.8659</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1871</v>
+        <v>-0.3879</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2198</v>
+        <v>-0.3005</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0326</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>1.228</v>
+        <v>0.4123</v>
       </c>
       <c r="K22" t="n">
-        <v>1.228</v>
+        <v>0.0384</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.3739</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0409</v>
+        <v>-0.8002</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0083</v>
+        <v>-0.3389</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0326</v>
+        <v>-0.4613</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.7867</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.2029</v>
+        <v>-1.0406</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4162</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9075</v>
+        <v>-0.052</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3262</v>
+        <v>-0.1538</v>
       </c>
       <c r="U22" t="n">
-        <v>1.2338</v>
+        <v>0.1018</v>
       </c>
       <c r="V22" t="n">
-        <v>0.23</v>
+        <v>-0.9376</v>
       </c>
       <c r="W22" t="n">
         <v>0.23</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. BLAK MOLLER</t>
+          <t>D. EFAMBE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.672</v>
+        <v>-2.6295</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6593</v>
+        <v>-3.8568</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0127</v>
+        <v>1.2274</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3879</v>
+        <v>1.1871</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3005</v>
+        <v>1.2198</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.0326</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4123</v>
+        <v>1.228</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0384</v>
+        <v>1.228</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3739</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8002</v>
+        <v>-0.0409</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3389</v>
+        <v>-0.0083</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4613</v>
+        <v>-0.0326</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.0406</v>
+        <v>-4.7867</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0406</v>
+        <v>-5.2029</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.4162</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.306</v>
+        <v>0.7402</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.261</v>
+        <v>-0.1119</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.045</v>
+        <v>0.8521</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9376</v>
+        <v>0.23</v>
       </c>
       <c r="W23" t="n">
         <v>0.23</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. ORRIT SERRANO</t>
+          <t>S. ROMERO SANCHEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.261</v>
+        <v>-4.955</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.4836</v>
+        <v>-3.3563</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2225</v>
+        <v>-1.5987</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.6778</v>
+        <v>-3.6488</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7356</v>
+        <v>-1.358</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.4135</v>
+        <v>-2.2909</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.0816</v>
+        <v>-1.73</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6584</v>
+        <v>-0.2922</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.7399</v>
+        <v>-1.4377</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5963000000000001</v>
+        <v>-1.9189</v>
       </c>
       <c r="N24" t="n">
-        <v>0.07729999999999999</v>
+        <v>-1.0657</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6735</v>
+        <v>-0.8532</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.7055</v>
+        <v>0.2081</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.3705</v>
+        <v>-1.2487</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3523</v>
+        <v>-0.7005</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.199</v>
+        <v>-0.3776</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5513</v>
+        <v>-0.3229</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.23</v>
+        <v>-0.8137</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.3975</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S. ROMERO SANCHEZ</t>
+          <t>D. ORRIT SERRANO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.7256</v>
+        <v>-5.3197</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.8921</v>
+        <v>-5.4836</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8336</v>
+        <v>0.1638</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.6488</v>
+        <v>-2.6778</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.358</v>
+        <v>0.7356</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.2909</v>
+        <v>-3.4135</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.73</v>
+        <v>-2.0816</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.2922</v>
+        <v>0.6584</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.4377</v>
+        <v>-2.7399</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.9189</v>
+        <v>-0.5963000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.0657</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8532</v>
+        <v>-0.6735</v>
       </c>
       <c r="P25" t="n">
-        <v>0.2081</v>
+        <v>-2.7055</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.2487</v>
+        <v>-4.3705</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4712</v>
+        <v>0.2936</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9134</v>
+        <v>-0.199</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5578</v>
+        <v>0.4926</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.8137</v>
+        <v>-0.23</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.8137</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="26">
@@ -2437,7 +2437,7 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-11.8193</v>
+        <v>-11.8194</v>
       </c>
       <c r="E26" t="n">
         <v>-14.7379</v>
@@ -2449,31 +2449,31 @@
         <v>-13.5941</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.04150000000000009</v>
+        <v>-0.04150000000000031</v>
       </c>
       <c r="I26" t="n">
         <v>-13.5527</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.1625</v>
+        <v>-5.162500000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>2.7162</v>
+        <v>2.716199999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>-7.878399999999999</v>
+        <v>-7.878400000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>-8.431800000000001</v>
+        <v>-8.431799999999999</v>
       </c>
       <c r="N26" t="n">
         <v>-2.7575</v>
       </c>
       <c r="O26" t="n">
-        <v>-5.673999999999999</v>
+        <v>-5.674</v>
       </c>
       <c r="P26" t="n">
-        <v>-6.2435</v>
+        <v>-6.243499999999999</v>
       </c>
       <c r="Q26" t="n">
         <v>-18.7306</v>
@@ -2482,13 +2482,13 @@
         <v>12.487</v>
       </c>
       <c r="S26" t="n">
-        <v>1.3666</v>
+        <v>1.3668</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.5023</v>
+        <v>-2.5024</v>
       </c>
       <c r="U26" t="n">
-        <v>3.8691</v>
+        <v>3.8692</v>
       </c>
       <c r="V26" t="n">
         <v>6.6513</v>
